--- a/output/2026-09-03_23_Italia_Basilicata_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-03_23_Italia_Basilicata_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ingrosso ferramenta e utensileria professionale, macchine e attrezzature per officine, rivenditore Fervi/SKF/USAG/Ravaglioli/DeWalt. Attiva dal 1975, Via della Fisica 26, Zona Industriale Potenza.</t>
+          <t>Ingrosso ferramenta e utensileria professionale, macchine e attrezzature per officine, rivenditore Fervi/SKF/USAG/Ravaglioli/DeWalt. Attiva dal 1975, Via della Fisica 26, Zona Industriale Potenza. [DUPLICATO — vedi anche: 2026-09-03_20_Italia_Basilicata_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ferramenta e utensileria industriale/professionale, rivenditore Beta, Makita, Dormer, Fag, Norton, Esab. Storica azienda dal 1935, Contrada Varco d'Izzo 14, Potenza.</t>
+          <t>Ferramenta e utensileria industriale/professionale, rivenditore Beta, Makita, Dormer, Fag, Norton, Esab. Storica azienda dal 1935, Contrada Varco d'Izzo 14, Potenza. [DUPLICATO — vedi anche: 2026-09-03_20_Italia_Basilicata_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,8 +573,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Vendita e noleggio gruppi elettrogeni, compressori, saldatrici, torri faro, attrezzature per cantieri/industria. Fondata 1990, Viggiano (PZ).</t>
@@ -661,7 +659,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ferramenta, utensileria industriale. Zona PIP, Lavello (PZ). Entita' giuridica distinta da Signore S.r.l. ma stesso gruppo familiare/brand: record separato per indirizzo/telefono diversi.</t>
+          <t>Ferramenta, utensileria industriale. Zona PIP, Lavello (PZ). Entita' giuridica distinta da Signore S.r.l. ma stesso gruppo familiare/brand: record separato per indirizzo/telefono diversi. [DUPLICATO — vedi anche: 2026-09-03_23_Italia_Basilicata_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -676,7 +674,6 @@
           <t>Murante Ignazio (Ferramenta - Forniture per Officine)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Potenza (PZ)</t>
@@ -692,7 +689,6 @@
           <t>0972 31831</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Ferramenta e forniture per officine, utensileria industriale. Via Balilla 50, Venosa (PZ). Nessun sito web trovato.</t>
@@ -730,7 +726,6 @@
           <t>0972 238063</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Ferramenta e utensileria (vernici, bricolage, antinfortunistica, elettroutensili). Melfi (PZ), P.IVA 00858270762. Focus prevalentemente retail/DIY oltre che professionale.</t>
@@ -768,7 +763,6 @@
           <t>0971 990127</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Ferramenta, abbigliamento da lavoro/sicurezza, bricolage, giardinaggio e carpenteria. Picerno (PZ). Fit settoriale debole: profilo prevalentemente retail/DIY piu' che distribuzione industriale B2B.</t>
@@ -806,10 +800,9 @@
           <t>0835 309141</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Commercio all'ingrosso macchine utensili, compressori, saldatrici, seghe circolari, attrezzature industriali/artigianali. Via dei Mestieri 45/C-D, Matera. ATECO 'Macchine utensili - commercio'.</t>
+          <t>Commercio all'ingrosso macchine utensili, compressori, saldatrici, seghe circolari, attrezzature industriali/artigianali. Via dei Mestieri 45/C-D, Matera. ATECO 'Macchine utensili - commercio'. [DUPLICATO — vedi anche: 2026-09-03_20_Italia_Basilicata_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -851,7 +844,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Vendita, noleggio e assistenza macchine/attrezzature movimento terra/edili, carrelli elevatori, utensileria (dealer Atlas Copco, Dynapac, Merlo). Matera, attiva dagli anni '80. Focus principale movimento terra/edile piu' che metalworking puro.</t>
+          <t>Vendita, noleggio e assistenza macchine/attrezzature movimento terra/edili, carrelli elevatori, utensileria (dealer Atlas Copco, Dynapac, Merlo). Matera, attiva dagli anni '80. Focus principale movimento terra/edile piu' che metalworking puro. [DUPLICATO — vedi anche: 2026-09-03_19_Italia_Basilicata_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -908,7 +901,6 @@
           <t>Ferramenta Bricolage / Maniglieria Natrella (Antonio Natrella)</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Matera (MT)</t>
@@ -924,7 +916,6 @@
           <t>0835 382051</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Ferramenta all'ingrosso, utensileria manuale ed elettrica, materiali da carpenteria. Via G.M. Trabaci 31 (C.C. Tre Torri), Matera.</t>
@@ -962,7 +953,6 @@
           <t>0835 381469</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Ingrosso/dettaglio accessori per infissi/serramenti in ferro-alluminio-legno, utensili per lavorazione ferro/alluminio/legno, forniture per fabbri e carpentieri. Zona PAIP2, Matera, attiva dal 1979.</t>

--- a/output/2026-09-03_23_Italia_Basilicata_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-03_23_Italia_Basilicata_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
